--- a/artfynd/A 39315-2026 artfynd.xlsx
+++ b/artfynd/A 39315-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,62 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13939286</v>
+        <v>137325886</v>
       </c>
       <c r="B2" t="n">
-        <v>12564</v>
+        <v>92430</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101691</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre barkplattbagge</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pytho abieticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>J.Sahlberg, 1875</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarntorpet, Jmt</t>
+          <t>Björndrolet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>431027</v>
+        <v>431066</v>
       </c>
       <c r="R2" t="n">
-        <v>7017371</v>
+        <v>7017413</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,17 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2008-08-20</t>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2008-08-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rapport finns hos länsstyrelsen. Låga P11</t>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,28 +775,1851 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137325886</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137328123</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92430</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>658</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Björndrolet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>431012</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7017220</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137328123</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137325797</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92159</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Björndrolet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>431060</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7017414</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137325797</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137328182</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92159</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Björndrolet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>431023</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7017219</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137328182</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137324486</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92173</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Björndrolet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>431062</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7017475</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137324486</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137325665</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92591</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Björndrolet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>431059</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7017414</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137325665</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137327928</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92591</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Björndrolet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>431007</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7017227</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137327928</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137324406</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92352</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1588</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Violmussling</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Trichaptum laricinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Björndrolet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>431056</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7017461</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137324406</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137326028</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92352</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1588</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Violmussling</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Trichaptum laricinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Björndrolet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>431063</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7017420</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137326028</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137328218</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92352</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1588</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Violmussling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Trichaptum laricinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Björndrolet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>431006</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7017230</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137328218</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137323753</v>
+      </c>
+      <c r="B12" t="n">
+        <v>75591</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Björndrolet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>431118</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7017441</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137323753</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137323030</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58033</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Björndrolet, Frisktorpet, Mörsil, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>431093</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7017402</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137323030</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13939286</v>
+      </c>
+      <c r="B14" t="n">
+        <v>12564</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>101691</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mindre barkplattbagge</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pytho abieticola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>J.Sahlberg, 1875</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kvarntorpet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>431027</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7017371</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2008-08-20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2008-08-20</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rapport finns hos länsstyrelsen. Låga P11</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>David Isaksson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>David Isaksson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY14" t="inlineStr">
         <is>
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/13939286</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137323446</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79514</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Björndrolet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>431107</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7017438</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137323446</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137328832</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79514</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Björndrolet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>431081</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7017179</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137328832</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137323089</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58201</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>266237</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita x tofsmes</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Björndrolet, Frisktorpet, Mörsil, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>431088</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7017418</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137323089</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137323413</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58201</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>266237</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita x tofsmes</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Björndrolet, Frisktorpet, Mörsil, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>431092</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7017426</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137323413</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39315-2026 artfynd.xlsx
+++ b/artfynd/A 39315-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ18"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137325886</v>
       </c>
       <c r="B2" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137328123</v>
       </c>
       <c r="B3" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137325797</v>
       </c>
       <c r="B4" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137328182</v>
       </c>
       <c r="B5" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,32 +1128,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137324486</v>
+        <v>137325665</v>
       </c>
       <c r="B6" t="n">
-        <v>92173</v>
+        <v>92594</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>431062</v>
+        <v>431059</v>
       </c>
       <c r="R6" t="n">
-        <v>7017475</v>
+        <v>7017414</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,16 +1234,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137324486</t>
+          <t>https://artportalen.se/Sighting/137325665</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137325665</v>
+        <v>137327928</v>
       </c>
       <c r="B7" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>431059</v>
+        <v>431007</v>
       </c>
       <c r="R7" t="n">
-        <v>7017414</v>
+        <v>7017227</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,16 +1346,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137325665</t>
+          <t>https://artportalen.se/Sighting/137327928</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137327928</v>
+        <v>137323753</v>
       </c>
       <c r="B8" t="n">
-        <v>92591</v>
+        <v>75594</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>431007</v>
+        <v>431118</v>
       </c>
       <c r="R8" t="n">
-        <v>7017227</v>
+        <v>7017441</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,16 +1458,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137327928</t>
+          <t>https://artportalen.se/Sighting/137323753</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137324406</v>
+        <v>137323030</v>
       </c>
       <c r="B9" t="n">
-        <v>92352</v>
+        <v>58034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,34 +1475,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björndrolet, Jmt</t>
+          <t>Björndrolet, Frisktorpet, Mörsil, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>431056</v>
+        <v>431093</v>
       </c>
       <c r="R9" t="n">
-        <v>7017461</v>
+        <v>7017402</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1570,51 +1574,65 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137324406</t>
+          <t>https://artportalen.se/Sighting/137323030</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137326028</v>
+        <v>13939286</v>
       </c>
       <c r="B10" t="n">
-        <v>92352</v>
+        <v>12564</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1588</v>
+        <v>101691</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Mindre barkplattbagge</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Pytho abieticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>J.Sahlberg, 1875</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björndrolet, Jmt</t>
+          <t>Kvarntorpet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>431063</v>
+        <v>431027</v>
       </c>
       <c r="R10" t="n">
-        <v>7017420</v>
+        <v>7017371</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,22 +1659,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2008-08-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2008-08-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rapport finns hos länsstyrelsen. Låga P11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,49 +1684,53 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fabian Pettersson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fabian Pettersson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137326028</t>
+          <t>https://artportalen.se/Sighting/13939286</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137328218</v>
+        <v>137323446</v>
       </c>
       <c r="B11" t="n">
-        <v>92352</v>
+        <v>79517</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1588</v>
+        <v>230405</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1740,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>431006</v>
+        <v>431107</v>
       </c>
       <c r="R11" t="n">
-        <v>7017230</v>
+        <v>7017438</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1775,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1785,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1794,38 +1811,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137328218</t>
+          <t>https://artportalen.se/Sighting/137323446</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137323753</v>
+        <v>137328832</v>
       </c>
       <c r="B12" t="n">
-        <v>75591</v>
+        <v>79517</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6426</v>
+        <v>230405</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1852,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>431118</v>
+        <v>431081</v>
       </c>
       <c r="R12" t="n">
-        <v>7017441</v>
+        <v>7017179</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1887,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1897,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1906,55 +1923,52 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137323753</t>
+          <t>https://artportalen.se/Sighting/137328832</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137323030</v>
+        <v>137323413</v>
       </c>
       <c r="B13" t="n">
-        <v>58033</v>
+        <v>58202</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>266237</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita x tofsmes</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Poecile montanus x Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Björndrolet, Frisktorpet, Mörsil, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>431093</v>
+        <v>431092</v>
       </c>
       <c r="R13" t="n">
-        <v>7017402</v>
+        <v>7017426</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1986,7 +2000,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,7 +2010,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2021,581 +2035,6 @@
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137323030</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13939286</v>
-      </c>
-      <c r="B14" t="n">
-        <v>12564</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>101691</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Mindre barkplattbagge</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Pytho abieticola</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>J.Sahlberg, 1875</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Kvarntorpet, Jmt</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>431027</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7017371</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Mörsil</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2008-08-20</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2008-08-20</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rapport finns hos länsstyrelsen. Låga P11</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>David Isaksson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>David Isaksson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/13939286</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>137323446</v>
-      </c>
-      <c r="B15" t="n">
-        <v>79514</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>230405</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Björndrolet, Jmt</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>431107</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7017438</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Mörsil</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Fabian Pettersson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Fabian Pettersson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137323446</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>137328832</v>
-      </c>
-      <c r="B16" t="n">
-        <v>79514</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>230405</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Björndrolet, Jmt</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>431081</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7017179</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Mörsil</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>17:12</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>17:12</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Fabian Pettersson</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Fabian Pettersson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137328832</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>137323089</v>
-      </c>
-      <c r="B17" t="n">
-        <v>58201</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>266237</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Talltita x tofsmes</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Björndrolet, Frisktorpet, Mörsil, Jmt</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>431088</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7017418</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Mörsil</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Fabian Pettersson</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Fabian Pettersson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137323089</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>137323413</v>
-      </c>
-      <c r="B18" t="n">
-        <v>58201</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>266237</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Talltita x tofsmes</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Poecile montanus x Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Björndrolet, Frisktorpet, Mörsil, Jmt</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>431092</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7017426</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Mörsil</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Fabian Pettersson</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Fabian Pettersson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137323413</t>
         </is>
@@ -2615,11 +2054,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39315-2026 artfynd.xlsx
+++ b/artfynd/A 39315-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137325886</v>
       </c>
       <c r="B2" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137328123</v>
       </c>
       <c r="B3" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137325797</v>
       </c>
       <c r="B4" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137328182</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137325665</v>
       </c>
       <c r="B6" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137327928</v>
       </c>
       <c r="B7" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 39315-2026 artfynd.xlsx
+++ b/artfynd/A 39315-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137325886</v>
       </c>
       <c r="B2" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137328123</v>
       </c>
       <c r="B3" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137325797</v>
       </c>
       <c r="B4" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137328182</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137325665</v>
       </c>
       <c r="B6" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137327928</v>
       </c>
       <c r="B7" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137323753</v>
       </c>
       <c r="B8" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137323030</v>
       </c>
       <c r="B9" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>137323446</v>
       </c>
       <c r="B11" t="n">
-        <v>79517</v>
+        <v>79522</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>137328832</v>
       </c>
       <c r="B12" t="n">
-        <v>79517</v>
+        <v>79522</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>137323413</v>
       </c>
       <c r="B13" t="n">
-        <v>58202</v>
+        <v>58203</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 39315-2026 artfynd.xlsx
+++ b/artfynd/A 39315-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137325886</v>
       </c>
       <c r="B2" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137328123</v>
       </c>
       <c r="B3" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137325797</v>
       </c>
       <c r="B4" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137328182</v>
       </c>
       <c r="B5" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137325665</v>
       </c>
       <c r="B6" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137327928</v>
       </c>
       <c r="B7" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137323753</v>
       </c>
       <c r="B8" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>137323446</v>
       </c>
       <c r="B11" t="n">
-        <v>79522</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>137328832</v>
       </c>
       <c r="B12" t="n">
-        <v>79522</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 39315-2026 artfynd.xlsx
+++ b/artfynd/A 39315-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137325886</v>
       </c>
       <c r="B2" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137328123</v>
       </c>
       <c r="B3" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137325797</v>
       </c>
       <c r="B4" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137328182</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137325665</v>
       </c>
       <c r="B6" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137327928</v>
       </c>
       <c r="B7" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>137323446</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79534</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>137328832</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79534</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 39315-2026 artfynd.xlsx
+++ b/artfynd/A 39315-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137325886</v>
       </c>
       <c r="B2" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137328123</v>
       </c>
       <c r="B3" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137325797</v>
       </c>
       <c r="B4" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137328182</v>
       </c>
       <c r="B5" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137325665</v>
       </c>
       <c r="B6" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137327928</v>
       </c>
       <c r="B7" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>137323446</v>
       </c>
       <c r="B11" t="n">
-        <v>79534</v>
+        <v>79536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>137328832</v>
       </c>
       <c r="B12" t="n">
-        <v>79534</v>
+        <v>79536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 39315-2026 artfynd.xlsx
+++ b/artfynd/A 39315-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137325886</v>
       </c>
       <c r="B2" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137328123</v>
       </c>
       <c r="B3" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137325797</v>
       </c>
       <c r="B4" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137328182</v>
       </c>
       <c r="B5" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137325665</v>
       </c>
       <c r="B6" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137327928</v>
       </c>
       <c r="B7" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137323753</v>
       </c>
       <c r="B8" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137323030</v>
       </c>
       <c r="B9" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>137323446</v>
       </c>
       <c r="B11" t="n">
-        <v>79536</v>
+        <v>79540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>137328832</v>
       </c>
       <c r="B12" t="n">
-        <v>79536</v>
+        <v>79540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>137323413</v>
       </c>
       <c r="B13" t="n">
-        <v>58203</v>
+        <v>58206</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
